--- a/clients/Poojamani/AY 2026-27/working_papers_tracker.xlsx
+++ b/clients/Poojamani/AY 2026-27/working_papers_tracker.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lokes\Desktop\TaxAuditAutomation\clients\Poojamani\AY 2026-27\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80653119-8AB3-476B-99D0-7E7ACAF77B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -100,14 +94,14 @@
     <t>Clause 35</t>
   </si>
   <si>
-    <t>Pending</t>
+    <t>Completed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,21 +138,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +182,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +216,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +250,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,19 +425,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -484,7 +460,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -495,7 +471,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -506,7 +482,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -517,7 +493,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -528,7 +504,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -539,7 +515,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -550,7 +526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -561,7 +537,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -572,7 +548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -583,7 +559,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -594,7 +570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>17</v>
       </c>

--- a/clients/Poojamani/AY 2026-27/working_papers_tracker.xlsx
+++ b/clients/Poojamani/AY 2026-27/working_papers_tracker.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="97">
+  <si>
+    <t>Category</t>
+  </si>
   <si>
     <t>Working Paper</t>
   </si>
@@ -22,6 +25,9 @@
     <t>Clause Reference</t>
   </si>
   <si>
+    <t>Linked Audit Procedure</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
@@ -34,6 +40,45 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>Basic Books Verification</t>
+  </si>
+  <si>
+    <t>GST Verification</t>
+  </si>
+  <si>
+    <t>TDS / TCS Verification</t>
+  </si>
+  <si>
+    <t>Statutory Dues and 43B Verification</t>
+  </si>
+  <si>
+    <t>Cash and Banking Verification</t>
+  </si>
+  <si>
+    <t>Loans and Deposits Verification</t>
+  </si>
+  <si>
+    <t>Related Party Verification</t>
+  </si>
+  <si>
+    <t>MSME Verification</t>
+  </si>
+  <si>
+    <t>Fixed Assets and Depreciation</t>
+  </si>
+  <si>
+    <t>Clause 44 Verification</t>
+  </si>
+  <si>
+    <t>Stock and Quantitative Details</t>
+  </si>
+  <si>
+    <t>Other Tax and Reporting</t>
+  </si>
+  <si>
+    <t>Final Audit Review</t>
+  </si>
+  <si>
     <t>Trial Balance Verification</t>
   </si>
   <si>
@@ -70,6 +115,87 @@
     <t>AIS/TIS Verification</t>
   </si>
   <si>
+    <t>Profit and Loss Verification</t>
+  </si>
+  <si>
+    <t>Balance Sheet Verification</t>
+  </si>
+  <si>
+    <t>Books Turnover vs GSTR-1 Sales Reconciliation</t>
+  </si>
+  <si>
+    <t>Books Purchases vs GSTR-2B Purchase Reconciliation</t>
+  </si>
+  <si>
+    <t>GST Input as per Books vs GSTR-2A / 2B</t>
+  </si>
+  <si>
+    <t>GSTR-1 vs GSTR-3B Reconciliation</t>
+  </si>
+  <si>
+    <t>TDS Payable and Paid Verification</t>
+  </si>
+  <si>
+    <t>TDS Receivable and Received Verification</t>
+  </si>
+  <si>
+    <t>TCS Verification</t>
+  </si>
+  <si>
+    <t>Section 43B Statutory Dues Verification</t>
+  </si>
+  <si>
+    <t>GST Liability vs GSTR-3B Filed Returns</t>
+  </si>
+  <si>
+    <t>TDS Deducted and Deposited Within Due Dates</t>
+  </si>
+  <si>
+    <t>PF / ESI Contribution and Return Verification</t>
+  </si>
+  <si>
+    <t>Bank Book Verification</t>
+  </si>
+  <si>
+    <t>Loans, Deposits and Specified Sums Verification</t>
+  </si>
+  <si>
+    <t>269SS / 269T / 269ST Compliance Verification</t>
+  </si>
+  <si>
+    <t>Related Party Transaction Verification</t>
+  </si>
+  <si>
+    <t>MSME Vendor and Delayed Payment Verification</t>
+  </si>
+  <si>
+    <t>Fixed Asset Register Verification</t>
+  </si>
+  <si>
+    <t>Depreciation as per Income Tax Act</t>
+  </si>
+  <si>
+    <t>Capital Asset Converted into Stock-in-Trade</t>
+  </si>
+  <si>
+    <t>GST Expenditure Break-up for Clause 44</t>
+  </si>
+  <si>
+    <t>Stock and Quantitative Details Verification</t>
+  </si>
+  <si>
+    <t>Tax Demand and Refund Verification</t>
+  </si>
+  <si>
+    <t>Form 61 / 61A / 61B Verification</t>
+  </si>
+  <si>
+    <t>Final Audit Observation Summary</t>
+  </si>
+  <si>
+    <t>Management Reply and Final Adjustments</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
@@ -94,7 +220,91 @@
     <t>Clause 35</t>
   </si>
   <si>
+    <t>Clause 11 / Clause 13 / Clause 40</t>
+  </si>
+  <si>
+    <t>Clause 13 / Clause 16 / Clause 21 / Clause 27 / Clause 40</t>
+  </si>
+  <si>
+    <t>Clause 11 / Clause 18 / Clause 22 / Clause 26 / Clause 31 / Clause 40</t>
+  </si>
+  <si>
+    <t>Clause 4 / Clause 44</t>
+  </si>
+  <si>
+    <t>Clause 27 / Clause 44</t>
+  </si>
+  <si>
+    <t>Clause 4 / Clause 41</t>
+  </si>
+  <si>
+    <t>Clause 21 / Clause 34</t>
+  </si>
+  <si>
+    <t>ITR Credit Verification / Clause 34</t>
+  </si>
+  <si>
+    <t>Clause 26</t>
+  </si>
+  <si>
+    <t>Clause 26 / Clause 41</t>
+  </si>
+  <si>
+    <t>Clause 26 / Clause 34</t>
+  </si>
+  <si>
+    <t>Clause 20 / Clause 26</t>
+  </si>
+  <si>
+    <t>Clause 21</t>
+  </si>
+  <si>
+    <t>General Audit Procedure</t>
+  </si>
+  <si>
+    <t>Clause 30 / Clause 31</t>
+  </si>
+  <si>
+    <t>Clause 22 / Clause 26</t>
+  </si>
+  <si>
+    <t>Clause 15</t>
+  </si>
+  <si>
+    <t>Clause 14 / Clause 35 / Clause 40</t>
+  </si>
+  <si>
+    <t>Clause 41</t>
+  </si>
+  <si>
+    <t>Clause 42</t>
+  </si>
+  <si>
+    <t>All Relevant Clauses</t>
+  </si>
+  <si>
+    <t>Final Review</t>
+  </si>
+  <si>
+    <t>Section 43B Verification</t>
+  </si>
+  <si>
+    <t>Bank Verification</t>
+  </si>
+  <si>
+    <t>Depreciation Verification</t>
+  </si>
+  <si>
+    <t>Clause 44 GST Expenditure Break-up</t>
+  </si>
+  <si>
+    <t>Tax Demand / Refund Verification</t>
+  </si>
+  <si>
     <t>Completed</t>
+  </si>
+  <si>
+    <t>Pending</t>
   </si>
 </sst>
 </file>
@@ -426,10 +636,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -448,137 +658,636 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
+        <v>92</v>
+      </c>
+      <c r="E36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B39" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
+      <c r="B41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
